--- a/EmailCompleteApp/EmailCompleteApp/doc/database.xlsx
+++ b/EmailCompleteApp/EmailCompleteApp/doc/database.xlsx
@@ -1,15 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15">
-  <x:fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <x:workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AutoEmailCompletion\EmailCompleteApp\EmailCompleteApp\doc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356F9365-1965-4F58-B2AE-9F99FA5A1E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="0" activeTab="0"/>
+    <x:workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="0" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Transportators" sheetId="4" r:id="rId4"/>
-    <x:sheet name="Clients" sheetId="6" r:id="rId6"/>
+    <x:sheet name="Transportators" sheetId="4" r:id="rId2"/>
+    <x:sheet name="Clients" sheetId="6" r:id="rId3"/>
+    <x:sheet name="Locations" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="162913"/>
@@ -17,6 +24,9 @@
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </x:ext>
+    <x:ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
@@ -69,7 +79,7 @@
     <x:t>cnp19392</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Client xyz </x:t>
+    <x:t>kriszti</x:t>
   </x:si>
   <x:si>
     <x:t>Adresa client 67</x:t>
@@ -88,12 +98,18 @@
   </x:si>
   <x:si>
     <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Satelit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Podului 18</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
@@ -106,17 +122,16 @@
       <x:scheme val="minor"/>
     </x:font>
     <x:font>
-      <x:vertAlign val="baseline"/>
+      <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
+      <x:color theme="1"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
-      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
-      <x:color theme="1"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -140,7 +155,7 @@
   </x:borders>
   <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -149,14 +164,8 @@
   </x:cellStyleXfs>
   <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +444,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -451,24 +460,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0100-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:H2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="17.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="19.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.855469" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.710938" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.855469" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19.710938" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15.285156" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8" s="1" customFormat="1">
+    <x:row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -494,7 +503,7 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:8">
+    <x:row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <x:c r="A2" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
@@ -530,6 +539,85 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0200-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:H2"/>
+  <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.710938" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.855469" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.855469" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.570312" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.425781" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.855469" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15.285156" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <x:c r="A2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H2" s="2">
+        <x:v>45928.5565899074</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
@@ -537,13 +625,9 @@
   <x:dimension ref="A1:H2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.424911" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17.853482" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="6.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="7" width="9.140625" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="15.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -554,49 +638,19 @@
       <x:c r="B1" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="H1" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
       <x:c r="A2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H2" s="2">
-        <x:v>45928.5565899074</x:v>
+        <x:v>45933.81851625</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
